--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374016</v>
+        <v>121374015</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407687</v>
+        <v>407686</v>
       </c>
       <c r="R4" t="n">
-        <v>7050641</v>
+        <v>7050640</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374022</v>
+        <v>121374023</v>
       </c>
       <c r="B5" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407793</v>
+        <v>407746</v>
       </c>
       <c r="R5" t="n">
-        <v>7050526</v>
+        <v>7050546</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374021</v>
+        <v>121374017</v>
       </c>
       <c r="B6" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407594</v>
+        <v>407695</v>
       </c>
       <c r="R6" t="n">
-        <v>7050460</v>
+        <v>7050648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1204,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374005</v>
+        <v>121373998</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407790</v>
+        <v>407587</v>
       </c>
       <c r="R7" t="n">
-        <v>7050600</v>
+        <v>7050786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374011</v>
+        <v>121374004</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407721</v>
+        <v>407798</v>
       </c>
       <c r="R8" t="n">
-        <v>7050507</v>
+        <v>7050463</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1422,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121373997</v>
+        <v>121374009</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407494</v>
+        <v>407792</v>
       </c>
       <c r="R9" t="n">
-        <v>7050775</v>
+        <v>7050525</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121374012</v>
+        <v>121374022</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407723</v>
+        <v>407793</v>
       </c>
       <c r="R10" t="n">
-        <v>7050509</v>
+        <v>7050526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,11 +1632,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121374013</v>
+        <v>121374011</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407744</v>
+        <v>407721</v>
       </c>
       <c r="R11" t="n">
-        <v>7050570</v>
+        <v>7050507</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121374017</v>
+        <v>121373997</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407695</v>
+        <v>407494</v>
       </c>
       <c r="R12" t="n">
-        <v>7050648</v>
+        <v>7050775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374007</v>
+        <v>121374021</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407801</v>
+        <v>407594</v>
       </c>
       <c r="R13" t="n">
-        <v>7050599</v>
+        <v>7050460</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,11 +1948,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121373998</v>
+        <v>121374016</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407587</v>
+        <v>407687</v>
       </c>
       <c r="R14" t="n">
-        <v>7050786</v>
+        <v>7050641</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374014</v>
+        <v>121374000</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407751</v>
+        <v>407556</v>
       </c>
       <c r="R15" t="n">
-        <v>7050584</v>
+        <v>7050508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121373999</v>
+        <v>121374012</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407558</v>
+        <v>407723</v>
       </c>
       <c r="R16" t="n">
-        <v>7050511</v>
+        <v>7050509</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374015</v>
+        <v>121374013</v>
       </c>
       <c r="B17" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2340,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407686</v>
+        <v>407744</v>
       </c>
       <c r="R17" t="n">
-        <v>7050640</v>
+        <v>7050570</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2375,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374001</v>
+        <v>121374007</v>
       </c>
       <c r="B18" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2447,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407610</v>
+        <v>407801</v>
       </c>
       <c r="R18" t="n">
-        <v>7050459</v>
+        <v>7050599</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2514,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374002</v>
+        <v>121374001</v>
       </c>
       <c r="B19" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407601</v>
+        <v>407610</v>
       </c>
       <c r="R19" t="n">
-        <v>7050461</v>
+        <v>7050459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2621,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374023</v>
+        <v>121374010</v>
       </c>
       <c r="B20" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2661,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407746</v>
+        <v>407753</v>
       </c>
       <c r="R20" t="n">
-        <v>7050546</v>
+        <v>7050520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,6 +2692,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374004</v>
+        <v>121373999</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407798</v>
+        <v>407558</v>
       </c>
       <c r="R21" t="n">
-        <v>7050463</v>
+        <v>7050511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374000</v>
+        <v>121374002</v>
       </c>
       <c r="B22" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407556</v>
+        <v>407601</v>
       </c>
       <c r="R22" t="n">
-        <v>7050508</v>
+        <v>7050461</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374010</v>
+        <v>121374014</v>
       </c>
       <c r="B23" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407753</v>
+        <v>407751</v>
       </c>
       <c r="R23" t="n">
-        <v>7050520</v>
+        <v>7050584</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374009</v>
+        <v>121374005</v>
       </c>
       <c r="B24" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407792</v>
+        <v>407790</v>
       </c>
       <c r="R24" t="n">
-        <v>7050525</v>
+        <v>7050600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374021</v>
+        <v>121374016</v>
       </c>
       <c r="B13" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407594</v>
+        <v>407687</v>
       </c>
       <c r="R13" t="n">
-        <v>7050460</v>
+        <v>7050641</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,6 +1948,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374016</v>
+        <v>121374021</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407687</v>
+        <v>407594</v>
       </c>
       <c r="R14" t="n">
-        <v>7050641</v>
+        <v>7050460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,11 +2055,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374016</v>
+        <v>121374021</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407687</v>
+        <v>407594</v>
       </c>
       <c r="R13" t="n">
-        <v>7050641</v>
+        <v>7050460</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,11 +1948,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374021</v>
+        <v>121374016</v>
       </c>
       <c r="B14" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407594</v>
+        <v>407687</v>
       </c>
       <c r="R14" t="n">
-        <v>7050460</v>
+        <v>7050641</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,6 +2050,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374015</v>
+        <v>121374001</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407686</v>
+        <v>407610</v>
       </c>
       <c r="R4" t="n">
-        <v>7050640</v>
+        <v>7050459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374017</v>
+        <v>121373998</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407695</v>
+        <v>407587</v>
       </c>
       <c r="R6" t="n">
-        <v>7050648</v>
+        <v>7050786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121373998</v>
+        <v>121374015</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407587</v>
+        <v>407686</v>
       </c>
       <c r="R7" t="n">
-        <v>7050786</v>
+        <v>7050640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374004</v>
+        <v>121374013</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407798</v>
+        <v>407744</v>
       </c>
       <c r="R8" t="n">
-        <v>7050463</v>
+        <v>7050570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121374009</v>
+        <v>121374004</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407792</v>
+        <v>407798</v>
       </c>
       <c r="R9" t="n">
-        <v>7050525</v>
+        <v>7050463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121374022</v>
+        <v>121374010</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407793</v>
+        <v>407753</v>
       </c>
       <c r="R10" t="n">
-        <v>7050526</v>
+        <v>7050520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,6 +1632,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121374011</v>
+        <v>121373999</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407721</v>
+        <v>407558</v>
       </c>
       <c r="R11" t="n">
-        <v>7050507</v>
+        <v>7050511</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121373997</v>
+        <v>121374005</v>
       </c>
       <c r="B12" t="n">
         <v>57351</v>
@@ -1805,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407494</v>
+        <v>407790</v>
       </c>
       <c r="R12" t="n">
-        <v>7050775</v>
+        <v>7050600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374021</v>
+        <v>121374017</v>
       </c>
       <c r="B13" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407594</v>
+        <v>407695</v>
       </c>
       <c r="R13" t="n">
-        <v>7050460</v>
+        <v>7050648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,6 +1953,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1984,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374016</v>
+        <v>121374012</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -2014,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407687</v>
+        <v>407723</v>
       </c>
       <c r="R14" t="n">
-        <v>7050641</v>
+        <v>7050509</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,7 +2064,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374000</v>
+        <v>121374014</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2121,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407556</v>
+        <v>407751</v>
       </c>
       <c r="R15" t="n">
-        <v>7050508</v>
+        <v>7050584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2171,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,7 +2198,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121374012</v>
+        <v>121374002</v>
       </c>
       <c r="B16" t="n">
         <v>57351</v>
@@ -2228,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407723</v>
+        <v>407601</v>
       </c>
       <c r="R16" t="n">
-        <v>7050509</v>
+        <v>7050461</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2278,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2305,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374013</v>
+        <v>121374007</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2335,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407744</v>
+        <v>407801</v>
       </c>
       <c r="R17" t="n">
-        <v>7050570</v>
+        <v>7050599</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2385,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,7 +2412,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374007</v>
+        <v>121374016</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2442,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407801</v>
+        <v>407687</v>
       </c>
       <c r="R18" t="n">
-        <v>7050599</v>
+        <v>7050641</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,7 +2519,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374001</v>
+        <v>121374011</v>
       </c>
       <c r="B19" t="n">
         <v>57351</v>
@@ -2549,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407610</v>
+        <v>407721</v>
       </c>
       <c r="R19" t="n">
-        <v>7050459</v>
+        <v>7050507</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,7 +2626,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374010</v>
+        <v>121373997</v>
       </c>
       <c r="B20" t="n">
         <v>57351</v>
@@ -2656,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407753</v>
+        <v>407494</v>
       </c>
       <c r="R20" t="n">
-        <v>7050520</v>
+        <v>7050775</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2706,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121373999</v>
+        <v>121374022</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2739,21 +2749,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407558</v>
+        <v>407793</v>
       </c>
       <c r="R21" t="n">
-        <v>7050511</v>
+        <v>7050526</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,11 +2809,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374002</v>
+        <v>121374021</v>
       </c>
       <c r="B22" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,21 +2851,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407601</v>
+        <v>407594</v>
       </c>
       <c r="R22" t="n">
-        <v>7050461</v>
+        <v>7050460</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,11 +2911,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374014</v>
+        <v>121374009</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407751</v>
+        <v>407792</v>
       </c>
       <c r="R23" t="n">
-        <v>7050584</v>
+        <v>7050525</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374005</v>
+        <v>121374000</v>
       </c>
       <c r="B24" t="n">
         <v>57351</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407790</v>
+        <v>407556</v>
       </c>
       <c r="R24" t="n">
-        <v>7050600</v>
+        <v>7050508</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374001</v>
+        <v>121373997</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407610</v>
+        <v>407494</v>
       </c>
       <c r="R4" t="n">
-        <v>7050459</v>
+        <v>7050775</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374023</v>
+        <v>121374016</v>
       </c>
       <c r="B5" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407746</v>
+        <v>407687</v>
       </c>
       <c r="R5" t="n">
-        <v>7050546</v>
+        <v>7050641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1102,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121373998</v>
+        <v>121373999</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407587</v>
+        <v>407558</v>
       </c>
       <c r="R6" t="n">
-        <v>7050786</v>
+        <v>7050511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374015</v>
+        <v>121374007</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407686</v>
+        <v>407801</v>
       </c>
       <c r="R7" t="n">
-        <v>7050640</v>
+        <v>7050599</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374013</v>
+        <v>121374000</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1382,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407744</v>
+        <v>407556</v>
       </c>
       <c r="R8" t="n">
-        <v>7050570</v>
+        <v>7050508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121374004</v>
+        <v>121374017</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1489,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407798</v>
+        <v>407695</v>
       </c>
       <c r="R9" t="n">
-        <v>7050463</v>
+        <v>7050648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1561,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121374010</v>
+        <v>121374002</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407753</v>
+        <v>407601</v>
       </c>
       <c r="R10" t="n">
-        <v>7050520</v>
+        <v>7050461</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1641,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,7 +1668,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121373999</v>
+        <v>121374012</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1703,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407558</v>
+        <v>407723</v>
       </c>
       <c r="R11" t="n">
-        <v>7050511</v>
+        <v>7050509</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1748,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121374005</v>
+        <v>121374010</v>
       </c>
       <c r="B12" t="n">
         <v>57351</v>
@@ -1810,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407790</v>
+        <v>407753</v>
       </c>
       <c r="R12" t="n">
-        <v>7050600</v>
+        <v>7050520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1855,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1882,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374017</v>
+        <v>121374005</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1917,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407695</v>
+        <v>407790</v>
       </c>
       <c r="R13" t="n">
-        <v>7050648</v>
+        <v>7050600</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1962,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374012</v>
+        <v>121374013</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -2024,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407723</v>
+        <v>407744</v>
       </c>
       <c r="R14" t="n">
-        <v>7050509</v>
+        <v>7050570</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374014</v>
+        <v>121374015</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2131,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407751</v>
+        <v>407686</v>
       </c>
       <c r="R15" t="n">
-        <v>7050584</v>
+        <v>7050640</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,7 +2176,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121374002</v>
+        <v>121373998</v>
       </c>
       <c r="B16" t="n">
         <v>57351</v>
@@ -2238,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407601</v>
+        <v>407587</v>
       </c>
       <c r="R16" t="n">
-        <v>7050461</v>
+        <v>7050786</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374007</v>
+        <v>121374022</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,21 +2326,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407801</v>
+        <v>407793</v>
       </c>
       <c r="R17" t="n">
-        <v>7050599</v>
+        <v>7050526</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,11 +2386,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,7 +2412,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374016</v>
+        <v>121374001</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407687</v>
+        <v>407610</v>
       </c>
       <c r="R18" t="n">
-        <v>7050641</v>
+        <v>7050459</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,7 +2519,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374011</v>
+        <v>121374009</v>
       </c>
       <c r="B19" t="n">
         <v>57351</v>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407721</v>
+        <v>407792</v>
       </c>
       <c r="R19" t="n">
-        <v>7050507</v>
+        <v>7050525</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121373997</v>
+        <v>121374021</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2642,21 +2642,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407494</v>
+        <v>407594</v>
       </c>
       <c r="R20" t="n">
-        <v>7050775</v>
+        <v>7050460</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,11 +2702,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2733,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374022</v>
+        <v>121374023</v>
       </c>
       <c r="B21" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407793</v>
+        <v>407746</v>
       </c>
       <c r="R21" t="n">
-        <v>7050526</v>
+        <v>7050546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374021</v>
+        <v>121374014</v>
       </c>
       <c r="B22" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407594</v>
+        <v>407751</v>
       </c>
       <c r="R22" t="n">
-        <v>7050460</v>
+        <v>7050584</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,6 +2906,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374009</v>
+        <v>121374004</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407792</v>
+        <v>407798</v>
       </c>
       <c r="R23" t="n">
-        <v>7050525</v>
+        <v>7050463</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374000</v>
+        <v>121374011</v>
       </c>
       <c r="B24" t="n">
         <v>57351</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407556</v>
+        <v>407721</v>
       </c>
       <c r="R24" t="n">
-        <v>7050508</v>
+        <v>7050507</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121373997</v>
+        <v>121374001</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407494</v>
+        <v>407610</v>
       </c>
       <c r="R4" t="n">
-        <v>7050775</v>
+        <v>7050459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374016</v>
+        <v>121374009</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407687</v>
+        <v>407792</v>
       </c>
       <c r="R5" t="n">
-        <v>7050641</v>
+        <v>7050525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121373999</v>
+        <v>121374011</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407558</v>
+        <v>407721</v>
       </c>
       <c r="R6" t="n">
-        <v>7050511</v>
+        <v>7050507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374007</v>
+        <v>121374023</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407801</v>
+        <v>407746</v>
       </c>
       <c r="R7" t="n">
-        <v>7050599</v>
+        <v>7050546</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1316,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374000</v>
+        <v>121373997</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1387,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407556</v>
+        <v>407494</v>
       </c>
       <c r="R8" t="n">
-        <v>7050508</v>
+        <v>7050775</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121374017</v>
+        <v>121373999</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1494,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407695</v>
+        <v>407558</v>
       </c>
       <c r="R9" t="n">
-        <v>7050648</v>
+        <v>7050511</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1529,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1556,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121374002</v>
+        <v>121373998</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407601</v>
+        <v>407587</v>
       </c>
       <c r="R10" t="n">
-        <v>7050461</v>
+        <v>7050786</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1775,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121374010</v>
+        <v>121374013</v>
       </c>
       <c r="B12" t="n">
         <v>57351</v>
@@ -1815,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407753</v>
+        <v>407744</v>
       </c>
       <c r="R12" t="n">
-        <v>7050520</v>
+        <v>7050570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374005</v>
+        <v>121374021</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1898,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1922,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407790</v>
+        <v>407594</v>
       </c>
       <c r="R13" t="n">
-        <v>7050600</v>
+        <v>7050460</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,11 +1953,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374013</v>
+        <v>121374022</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2029,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407744</v>
+        <v>407793</v>
       </c>
       <c r="R14" t="n">
-        <v>7050570</v>
+        <v>7050526</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,11 +2055,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374015</v>
+        <v>121374002</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2136,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407686</v>
+        <v>407601</v>
       </c>
       <c r="R15" t="n">
-        <v>7050640</v>
+        <v>7050461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121373998</v>
+        <v>121374017</v>
       </c>
       <c r="B16" t="n">
         <v>57351</v>
@@ -2243,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407587</v>
+        <v>407695</v>
       </c>
       <c r="R16" t="n">
-        <v>7050786</v>
+        <v>7050648</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374022</v>
+        <v>121374005</v>
       </c>
       <c r="B17" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2326,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407793</v>
+        <v>407790</v>
       </c>
       <c r="R17" t="n">
-        <v>7050526</v>
+        <v>7050600</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,6 +2371,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374001</v>
+        <v>121374004</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2452,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407610</v>
+        <v>407798</v>
       </c>
       <c r="R18" t="n">
-        <v>7050459</v>
+        <v>7050463</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374009</v>
+        <v>121374016</v>
       </c>
       <c r="B19" t="n">
         <v>57351</v>
@@ -2559,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407792</v>
+        <v>407687</v>
       </c>
       <c r="R19" t="n">
-        <v>7050525</v>
+        <v>7050641</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2589,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374021</v>
+        <v>121374007</v>
       </c>
       <c r="B20" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2642,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407594</v>
+        <v>407801</v>
       </c>
       <c r="R20" t="n">
-        <v>7050460</v>
+        <v>7050599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,6 +2692,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374023</v>
+        <v>121374014</v>
       </c>
       <c r="B21" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2768,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407746</v>
+        <v>407751</v>
       </c>
       <c r="R21" t="n">
-        <v>7050546</v>
+        <v>7050584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,6 +2799,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374014</v>
+        <v>121374010</v>
       </c>
       <c r="B22" t="n">
         <v>57351</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407751</v>
+        <v>407753</v>
       </c>
       <c r="R22" t="n">
-        <v>7050584</v>
+        <v>7050520</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374004</v>
+        <v>121374000</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407798</v>
+        <v>407556</v>
       </c>
       <c r="R23" t="n">
-        <v>7050463</v>
+        <v>7050508</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374011</v>
+        <v>121374015</v>
       </c>
       <c r="B24" t="n">
         <v>57351</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407721</v>
+        <v>407686</v>
       </c>
       <c r="R24" t="n">
-        <v>7050507</v>
+        <v>7050640</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374001</v>
+        <v>121374017</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407610</v>
+        <v>407695</v>
       </c>
       <c r="R4" t="n">
-        <v>7050459</v>
+        <v>7050648</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374009</v>
+        <v>121374010</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407792</v>
+        <v>407753</v>
       </c>
       <c r="R5" t="n">
-        <v>7050525</v>
+        <v>7050520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374011</v>
+        <v>121374009</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407721</v>
+        <v>407792</v>
       </c>
       <c r="R6" t="n">
-        <v>7050507</v>
+        <v>7050525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374023</v>
+        <v>121374002</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407746</v>
+        <v>407601</v>
       </c>
       <c r="R7" t="n">
-        <v>7050546</v>
+        <v>7050461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,6 +1316,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121373997</v>
+        <v>121374023</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407494</v>
+        <v>407746</v>
       </c>
       <c r="R8" t="n">
-        <v>7050775</v>
+        <v>7050546</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,11 +1423,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121373999</v>
+        <v>121373997</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407558</v>
+        <v>407494</v>
       </c>
       <c r="R9" t="n">
-        <v>7050511</v>
+        <v>7050775</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121373998</v>
+        <v>121374013</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407587</v>
+        <v>407744</v>
       </c>
       <c r="R10" t="n">
-        <v>7050786</v>
+        <v>7050570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121374012</v>
+        <v>121374004</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407723</v>
+        <v>407798</v>
       </c>
       <c r="R11" t="n">
-        <v>7050509</v>
+        <v>7050463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121374013</v>
+        <v>121374001</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407744</v>
+        <v>407610</v>
       </c>
       <c r="R12" t="n">
-        <v>7050570</v>
+        <v>7050459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,7 +1880,7 @@
         <v>121374021</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374022</v>
+        <v>121374007</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407793</v>
+        <v>407801</v>
       </c>
       <c r="R14" t="n">
-        <v>7050526</v>
+        <v>7050599</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,6 +2055,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374002</v>
+        <v>121374005</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407601</v>
+        <v>407790</v>
       </c>
       <c r="R15" t="n">
-        <v>7050461</v>
+        <v>7050600</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121374017</v>
+        <v>121374012</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2228,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407695</v>
+        <v>407723</v>
       </c>
       <c r="R16" t="n">
-        <v>7050648</v>
+        <v>7050509</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374005</v>
+        <v>121374016</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407790</v>
+        <v>407687</v>
       </c>
       <c r="R17" t="n">
-        <v>7050600</v>
+        <v>7050641</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374004</v>
+        <v>121373999</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2442,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407798</v>
+        <v>407558</v>
       </c>
       <c r="R18" t="n">
-        <v>7050463</v>
+        <v>7050511</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2487,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374016</v>
+        <v>121374000</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2549,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407687</v>
+        <v>407556</v>
       </c>
       <c r="R19" t="n">
-        <v>7050641</v>
+        <v>7050508</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2594,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374007</v>
+        <v>121374011</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407801</v>
+        <v>407721</v>
       </c>
       <c r="R20" t="n">
-        <v>7050599</v>
+        <v>7050507</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374014</v>
+        <v>121374015</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407751</v>
+        <v>407686</v>
       </c>
       <c r="R21" t="n">
-        <v>7050584</v>
+        <v>7050640</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2808,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374010</v>
+        <v>121374014</v>
       </c>
       <c r="B22" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407753</v>
+        <v>407751</v>
       </c>
       <c r="R22" t="n">
-        <v>7050520</v>
+        <v>7050584</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2915,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374000</v>
+        <v>121374022</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2958,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407556</v>
+        <v>407793</v>
       </c>
       <c r="R23" t="n">
-        <v>7050508</v>
+        <v>7050526</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,11 +3018,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374015</v>
+        <v>121373998</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407686</v>
+        <v>407587</v>
       </c>
       <c r="R24" t="n">
-        <v>7050640</v>
+        <v>7050786</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374017</v>
+        <v>121373999</v>
       </c>
       <c r="B4" t="n">
         <v>57354</v>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407695</v>
+        <v>407558</v>
       </c>
       <c r="R4" t="n">
-        <v>7050648</v>
+        <v>7050511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374010</v>
+        <v>121374012</v>
       </c>
       <c r="B5" t="n">
         <v>57354</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407753</v>
+        <v>407723</v>
       </c>
       <c r="R5" t="n">
-        <v>7050520</v>
+        <v>7050509</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374009</v>
+        <v>121374014</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407792</v>
+        <v>407751</v>
       </c>
       <c r="R6" t="n">
-        <v>7050525</v>
+        <v>7050584</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374002</v>
+        <v>121374017</v>
       </c>
       <c r="B7" t="n">
         <v>57354</v>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407601</v>
+        <v>407695</v>
       </c>
       <c r="R7" t="n">
-        <v>7050461</v>
+        <v>7050648</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374023</v>
+        <v>121374000</v>
       </c>
       <c r="B8" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407746</v>
+        <v>407556</v>
       </c>
       <c r="R8" t="n">
-        <v>7050546</v>
+        <v>7050508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,6 +1423,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121373997</v>
+        <v>121374022</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407494</v>
+        <v>407793</v>
       </c>
       <c r="R9" t="n">
-        <v>7050775</v>
+        <v>7050526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,11 +1530,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,7 +1556,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121374013</v>
+        <v>121374009</v>
       </c>
       <c r="B10" t="n">
         <v>57354</v>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407744</v>
+        <v>407792</v>
       </c>
       <c r="R10" t="n">
-        <v>7050570</v>
+        <v>7050525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121374004</v>
+        <v>121374013</v>
       </c>
       <c r="B11" t="n">
         <v>57354</v>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407798</v>
+        <v>407744</v>
       </c>
       <c r="R11" t="n">
-        <v>7050463</v>
+        <v>7050570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121374001</v>
+        <v>121374005</v>
       </c>
       <c r="B12" t="n">
         <v>57354</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407610</v>
+        <v>407790</v>
       </c>
       <c r="R12" t="n">
-        <v>7050459</v>
+        <v>7050600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374021</v>
+        <v>121374002</v>
       </c>
       <c r="B13" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407594</v>
+        <v>407601</v>
       </c>
       <c r="R13" t="n">
-        <v>7050460</v>
+        <v>7050461</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,6 +1953,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,7 +1984,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374007</v>
+        <v>121374010</v>
       </c>
       <c r="B14" t="n">
         <v>57354</v>
@@ -2019,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407801</v>
+        <v>407753</v>
       </c>
       <c r="R14" t="n">
-        <v>7050599</v>
+        <v>7050520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2064,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374005</v>
+        <v>121374015</v>
       </c>
       <c r="B15" t="n">
         <v>57354</v>
@@ -2126,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407790</v>
+        <v>407686</v>
       </c>
       <c r="R15" t="n">
-        <v>7050600</v>
+        <v>7050640</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,7 +2198,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121374012</v>
+        <v>121373997</v>
       </c>
       <c r="B16" t="n">
         <v>57354</v>
@@ -2233,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407723</v>
+        <v>407494</v>
       </c>
       <c r="R16" t="n">
-        <v>7050509</v>
+        <v>7050775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374016</v>
+        <v>121374023</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407687</v>
+        <v>407746</v>
       </c>
       <c r="R17" t="n">
-        <v>7050641</v>
+        <v>7050546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,11 +2381,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121373999</v>
+        <v>121374021</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407558</v>
+        <v>407594</v>
       </c>
       <c r="R18" t="n">
-        <v>7050511</v>
+        <v>7050460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,11 +2483,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374000</v>
+        <v>121374007</v>
       </c>
       <c r="B19" t="n">
         <v>57354</v>
@@ -2554,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407556</v>
+        <v>407801</v>
       </c>
       <c r="R19" t="n">
-        <v>7050508</v>
+        <v>7050599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374015</v>
+        <v>121374016</v>
       </c>
       <c r="B21" t="n">
         <v>57354</v>
@@ -2768,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407686</v>
+        <v>407687</v>
       </c>
       <c r="R21" t="n">
-        <v>7050640</v>
+        <v>7050641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374014</v>
+        <v>121373998</v>
       </c>
       <c r="B22" t="n">
         <v>57354</v>
@@ -2875,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407751</v>
+        <v>407587</v>
       </c>
       <c r="R22" t="n">
-        <v>7050584</v>
+        <v>7050786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374022</v>
+        <v>121374004</v>
       </c>
       <c r="B23" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2958,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2982,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407793</v>
+        <v>407798</v>
       </c>
       <c r="R23" t="n">
-        <v>7050526</v>
+        <v>7050463</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,6 +3013,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121373998</v>
+        <v>121374001</v>
       </c>
       <c r="B24" t="n">
         <v>57354</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407587</v>
+        <v>407610</v>
       </c>
       <c r="R24" t="n">
-        <v>7050786</v>
+        <v>7050459</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121373999</v>
+        <v>121374001</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407558</v>
+        <v>407610</v>
       </c>
       <c r="R4" t="n">
-        <v>7050511</v>
+        <v>7050459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374012</v>
+        <v>121374015</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407723</v>
+        <v>407686</v>
       </c>
       <c r="R5" t="n">
-        <v>7050509</v>
+        <v>7050640</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374014</v>
+        <v>121374012</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407751</v>
+        <v>407723</v>
       </c>
       <c r="R6" t="n">
-        <v>7050584</v>
+        <v>7050509</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374017</v>
+        <v>121374021</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407695</v>
+        <v>407594</v>
       </c>
       <c r="R7" t="n">
-        <v>7050648</v>
+        <v>7050460</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1316,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374000</v>
+        <v>121374007</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407556</v>
+        <v>407801</v>
       </c>
       <c r="R8" t="n">
-        <v>7050508</v>
+        <v>7050599</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121374022</v>
+        <v>121374004</v>
       </c>
       <c r="B9" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407793</v>
+        <v>407798</v>
       </c>
       <c r="R9" t="n">
-        <v>7050526</v>
+        <v>7050463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,6 +1525,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121374009</v>
+        <v>121374022</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407792</v>
+        <v>407793</v>
       </c>
       <c r="R10" t="n">
-        <v>7050525</v>
+        <v>7050526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,11 +1632,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121374013</v>
+        <v>121374002</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407744</v>
+        <v>407601</v>
       </c>
       <c r="R11" t="n">
-        <v>7050570</v>
+        <v>7050461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1738,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121374005</v>
+        <v>121373998</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407790</v>
+        <v>407587</v>
       </c>
       <c r="R12" t="n">
-        <v>7050600</v>
+        <v>7050786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374002</v>
+        <v>121374014</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407601</v>
+        <v>407751</v>
       </c>
       <c r="R13" t="n">
-        <v>7050461</v>
+        <v>7050584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1952,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374010</v>
+        <v>121374005</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407753</v>
+        <v>407790</v>
       </c>
       <c r="R14" t="n">
-        <v>7050520</v>
+        <v>7050600</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2059,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374015</v>
+        <v>121374017</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407686</v>
+        <v>407695</v>
       </c>
       <c r="R15" t="n">
-        <v>7050640</v>
+        <v>7050648</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,7 +2166,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121373997</v>
+        <v>121374013</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407494</v>
+        <v>407744</v>
       </c>
       <c r="R16" t="n">
-        <v>7050775</v>
+        <v>7050570</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374023</v>
+        <v>121373999</v>
       </c>
       <c r="B17" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407746</v>
+        <v>407558</v>
       </c>
       <c r="R17" t="n">
-        <v>7050546</v>
+        <v>7050511</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,6 +2376,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374021</v>
+        <v>121374000</v>
       </c>
       <c r="B18" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407594</v>
+        <v>407556</v>
       </c>
       <c r="R18" t="n">
-        <v>7050460</v>
+        <v>7050508</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,6 +2483,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374007</v>
+        <v>121374010</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2549,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407801</v>
+        <v>407753</v>
       </c>
       <c r="R19" t="n">
-        <v>7050599</v>
+        <v>7050520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2594,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374011</v>
+        <v>121374016</v>
       </c>
       <c r="B20" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407721</v>
+        <v>407687</v>
       </c>
       <c r="R20" t="n">
-        <v>7050507</v>
+        <v>7050641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374016</v>
+        <v>121373997</v>
       </c>
       <c r="B21" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407687</v>
+        <v>407494</v>
       </c>
       <c r="R21" t="n">
-        <v>7050641</v>
+        <v>7050775</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2808,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121373998</v>
+        <v>121374023</v>
       </c>
       <c r="B22" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,21 +2851,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407587</v>
+        <v>407746</v>
       </c>
       <c r="R22" t="n">
-        <v>7050786</v>
+        <v>7050546</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,11 +2911,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374004</v>
+        <v>121374011</v>
       </c>
       <c r="B23" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407798</v>
+        <v>407721</v>
       </c>
       <c r="R23" t="n">
-        <v>7050463</v>
+        <v>7050507</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374001</v>
+        <v>121374009</v>
       </c>
       <c r="B24" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407610</v>
+        <v>407792</v>
       </c>
       <c r="R24" t="n">
-        <v>7050459</v>
+        <v>7050525</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374001</v>
+        <v>121374023</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407610</v>
+        <v>407746</v>
       </c>
       <c r="R4" t="n">
-        <v>7050459</v>
+        <v>7050546</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,11 +995,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1024,7 @@
         <v>121374015</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374012</v>
+        <v>121374016</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407723</v>
+        <v>407687</v>
       </c>
       <c r="R6" t="n">
-        <v>7050509</v>
+        <v>7050641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374021</v>
+        <v>121374004</v>
       </c>
       <c r="B7" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407594</v>
+        <v>407798</v>
       </c>
       <c r="R7" t="n">
-        <v>7050460</v>
+        <v>7050463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,6 +1311,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374007</v>
+        <v>121374011</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407801</v>
+        <v>407721</v>
       </c>
       <c r="R8" t="n">
-        <v>7050599</v>
+        <v>7050507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121374004</v>
+        <v>121374007</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407798</v>
+        <v>407801</v>
       </c>
       <c r="R9" t="n">
-        <v>7050463</v>
+        <v>7050599</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121374022</v>
+        <v>121373997</v>
       </c>
       <c r="B10" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407793</v>
+        <v>407494</v>
       </c>
       <c r="R10" t="n">
-        <v>7050526</v>
+        <v>7050775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,6 +1632,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121374002</v>
+        <v>121374005</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407601</v>
+        <v>407790</v>
       </c>
       <c r="R11" t="n">
-        <v>7050461</v>
+        <v>7050600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1773,7 @@
         <v>121373998</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1872,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374014</v>
+        <v>121374001</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407751</v>
+        <v>407610</v>
       </c>
       <c r="R13" t="n">
-        <v>7050584</v>
+        <v>7050459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1957,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374005</v>
+        <v>121374010</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407790</v>
+        <v>407753</v>
       </c>
       <c r="R14" t="n">
-        <v>7050600</v>
+        <v>7050520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2064,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374017</v>
+        <v>121374012</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407695</v>
+        <v>407723</v>
       </c>
       <c r="R15" t="n">
-        <v>7050648</v>
+        <v>7050509</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121374013</v>
+        <v>121373999</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407744</v>
+        <v>407558</v>
       </c>
       <c r="R16" t="n">
-        <v>7050570</v>
+        <v>7050511</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2278,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121373999</v>
+        <v>121374021</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407558</v>
+        <v>407594</v>
       </c>
       <c r="R17" t="n">
-        <v>7050511</v>
+        <v>7050460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,11 +2381,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374000</v>
+        <v>121374009</v>
       </c>
       <c r="B18" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407556</v>
+        <v>407792</v>
       </c>
       <c r="R18" t="n">
-        <v>7050508</v>
+        <v>7050525</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374010</v>
+        <v>121374017</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407753</v>
+        <v>407695</v>
       </c>
       <c r="R19" t="n">
-        <v>7050520</v>
+        <v>7050648</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374016</v>
+        <v>121374000</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407687</v>
+        <v>407556</v>
       </c>
       <c r="R20" t="n">
-        <v>7050641</v>
+        <v>7050508</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121373997</v>
+        <v>121374014</v>
       </c>
       <c r="B21" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407494</v>
+        <v>407751</v>
       </c>
       <c r="R21" t="n">
-        <v>7050775</v>
+        <v>7050584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374023</v>
+        <v>121374002</v>
       </c>
       <c r="B22" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407746</v>
+        <v>407601</v>
       </c>
       <c r="R22" t="n">
-        <v>7050546</v>
+        <v>7050461</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,6 +2911,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374011</v>
+        <v>121374022</v>
       </c>
       <c r="B23" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2958,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407721</v>
+        <v>407793</v>
       </c>
       <c r="R23" t="n">
-        <v>7050507</v>
+        <v>7050526</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,11 +3018,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374009</v>
+        <v>121374013</v>
       </c>
       <c r="B24" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407792</v>
+        <v>407744</v>
       </c>
       <c r="R24" t="n">
-        <v>7050525</v>
+        <v>7050570</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374023</v>
+        <v>121374000</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407746</v>
+        <v>407556</v>
       </c>
       <c r="R4" t="n">
-        <v>7050546</v>
+        <v>7050508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,6 +995,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374015</v>
+        <v>121374005</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407686</v>
+        <v>407790</v>
       </c>
       <c r="R5" t="n">
-        <v>7050640</v>
+        <v>7050600</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374016</v>
+        <v>121374021</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407687</v>
+        <v>407594</v>
       </c>
       <c r="R6" t="n">
-        <v>7050641</v>
+        <v>7050460</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,11 +1209,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374004</v>
+        <v>121374016</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407798</v>
+        <v>407687</v>
       </c>
       <c r="R7" t="n">
-        <v>7050463</v>
+        <v>7050641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374011</v>
+        <v>121374022</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407721</v>
+        <v>407793</v>
       </c>
       <c r="R8" t="n">
-        <v>7050507</v>
+        <v>7050526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,11 +1418,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121374007</v>
+        <v>121374012</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1489,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407801</v>
+        <v>407723</v>
       </c>
       <c r="R9" t="n">
-        <v>7050599</v>
+        <v>7050509</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1524,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121373997</v>
+        <v>121374009</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1596,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407494</v>
+        <v>407792</v>
       </c>
       <c r="R10" t="n">
-        <v>7050775</v>
+        <v>7050525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121374005</v>
+        <v>121374013</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1703,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407790</v>
+        <v>407744</v>
       </c>
       <c r="R11" t="n">
-        <v>7050600</v>
+        <v>7050570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1738,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1765,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121373998</v>
+        <v>121373997</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1810,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407587</v>
+        <v>407494</v>
       </c>
       <c r="R12" t="n">
-        <v>7050786</v>
+        <v>7050775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1845,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374001</v>
+        <v>121374004</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1917,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407610</v>
+        <v>407798</v>
       </c>
       <c r="R13" t="n">
-        <v>7050459</v>
+        <v>7050463</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1952,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374010</v>
+        <v>121374023</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2000,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407753</v>
+        <v>407746</v>
       </c>
       <c r="R14" t="n">
-        <v>7050520</v>
+        <v>7050546</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,11 +2055,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374012</v>
+        <v>121373998</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2131,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407723</v>
+        <v>407587</v>
       </c>
       <c r="R15" t="n">
-        <v>7050509</v>
+        <v>7050786</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,7 +2161,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121373999</v>
+        <v>121374014</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2238,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407558</v>
+        <v>407751</v>
       </c>
       <c r="R16" t="n">
-        <v>7050511</v>
+        <v>7050584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374021</v>
+        <v>121374015</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407594</v>
+        <v>407686</v>
       </c>
       <c r="R17" t="n">
-        <v>7050460</v>
+        <v>7050640</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,6 +2371,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374009</v>
+        <v>121374010</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2447,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407792</v>
+        <v>407753</v>
       </c>
       <c r="R18" t="n">
-        <v>7050525</v>
+        <v>7050520</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374017</v>
+        <v>121374007</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2554,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407695</v>
+        <v>407801</v>
       </c>
       <c r="R19" t="n">
-        <v>7050648</v>
+        <v>7050599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374000</v>
+        <v>121374017</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2661,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407556</v>
+        <v>407695</v>
       </c>
       <c r="R20" t="n">
-        <v>7050508</v>
+        <v>7050648</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2696,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374014</v>
+        <v>121374001</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2768,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407751</v>
+        <v>407610</v>
       </c>
       <c r="R21" t="n">
-        <v>7050584</v>
+        <v>7050459</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2803,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374002</v>
+        <v>121374011</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2875,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407601</v>
+        <v>407721</v>
       </c>
       <c r="R22" t="n">
-        <v>7050461</v>
+        <v>7050507</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2942,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374022</v>
+        <v>121373999</v>
       </c>
       <c r="B23" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2958,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2982,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407793</v>
+        <v>407558</v>
       </c>
       <c r="R23" t="n">
-        <v>7050526</v>
+        <v>7050511</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,6 +3013,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374013</v>
+        <v>121374002</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407744</v>
+        <v>407601</v>
       </c>
       <c r="R24" t="n">
-        <v>7050570</v>
+        <v>7050461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374005</v>
+        <v>121374016</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407790</v>
+        <v>407687</v>
       </c>
       <c r="R5" t="n">
-        <v>7050600</v>
+        <v>7050641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374021</v>
+        <v>121374001</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407594</v>
+        <v>407610</v>
       </c>
       <c r="R6" t="n">
-        <v>7050460</v>
+        <v>7050459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,6 +1209,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374016</v>
+        <v>121374010</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407687</v>
+        <v>407753</v>
       </c>
       <c r="R7" t="n">
-        <v>7050641</v>
+        <v>7050520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1320,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374022</v>
+        <v>121374017</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407793</v>
+        <v>407695</v>
       </c>
       <c r="R8" t="n">
-        <v>7050526</v>
+        <v>7050648</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,6 +1423,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121374012</v>
+        <v>121374011</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1484,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407723</v>
+        <v>407721</v>
       </c>
       <c r="R9" t="n">
-        <v>7050509</v>
+        <v>7050507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1534,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,7 +1561,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121374009</v>
+        <v>121374012</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1591,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407792</v>
+        <v>407723</v>
       </c>
       <c r="R10" t="n">
-        <v>7050525</v>
+        <v>7050509</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1668,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121374013</v>
+        <v>121373997</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1698,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407744</v>
+        <v>407494</v>
       </c>
       <c r="R11" t="n">
-        <v>7050570</v>
+        <v>7050775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121373997</v>
+        <v>121374014</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1805,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407494</v>
+        <v>407751</v>
       </c>
       <c r="R12" t="n">
-        <v>7050775</v>
+        <v>7050584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,7 +1882,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374004</v>
+        <v>121374005</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1912,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407798</v>
+        <v>407790</v>
       </c>
       <c r="R13" t="n">
-        <v>7050463</v>
+        <v>7050600</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1962,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374023</v>
+        <v>121374022</v>
       </c>
       <c r="B14" t="n">
         <v>90738</v>
@@ -2019,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407746</v>
+        <v>407793</v>
       </c>
       <c r="R14" t="n">
-        <v>7050546</v>
+        <v>7050526</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121373998</v>
+        <v>121374013</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2121,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407587</v>
+        <v>407744</v>
       </c>
       <c r="R15" t="n">
-        <v>7050786</v>
+        <v>7050570</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2171,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121374014</v>
+        <v>121374023</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407751</v>
+        <v>407746</v>
       </c>
       <c r="R16" t="n">
-        <v>7050584</v>
+        <v>7050546</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,11 +2274,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374015</v>
+        <v>121374007</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2335,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407686</v>
+        <v>407801</v>
       </c>
       <c r="R17" t="n">
-        <v>7050640</v>
+        <v>7050599</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374010</v>
+        <v>121374009</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2442,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407753</v>
+        <v>407792</v>
       </c>
       <c r="R18" t="n">
-        <v>7050520</v>
+        <v>7050525</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2487,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374007</v>
+        <v>121374021</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2530,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407801</v>
+        <v>407594</v>
       </c>
       <c r="R19" t="n">
-        <v>7050599</v>
+        <v>7050460</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2585,11 +2590,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374017</v>
+        <v>121374004</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407695</v>
+        <v>407798</v>
       </c>
       <c r="R20" t="n">
-        <v>7050648</v>
+        <v>7050463</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374001</v>
+        <v>121373999</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407610</v>
+        <v>407558</v>
       </c>
       <c r="R21" t="n">
-        <v>7050459</v>
+        <v>7050511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374011</v>
+        <v>121373998</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407721</v>
+        <v>407587</v>
       </c>
       <c r="R22" t="n">
-        <v>7050507</v>
+        <v>7050786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121373999</v>
+        <v>121374015</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407558</v>
+        <v>407686</v>
       </c>
       <c r="R23" t="n">
-        <v>7050511</v>
+        <v>7050640</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374000</v>
+        <v>121374022</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407556</v>
+        <v>407793</v>
       </c>
       <c r="R4" t="n">
-        <v>7050508</v>
+        <v>7050526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,11 +995,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374016</v>
+        <v>121374001</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407687</v>
+        <v>407610</v>
       </c>
       <c r="R5" t="n">
-        <v>7050641</v>
+        <v>7050459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374001</v>
+        <v>121374016</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407610</v>
+        <v>407687</v>
       </c>
       <c r="R6" t="n">
-        <v>7050459</v>
+        <v>7050641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1347,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121374017</v>
+        <v>121373997</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1387,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407695</v>
+        <v>407494</v>
       </c>
       <c r="R8" t="n">
-        <v>7050648</v>
+        <v>7050775</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121374011</v>
+        <v>121374004</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1494,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407721</v>
+        <v>407798</v>
       </c>
       <c r="R9" t="n">
-        <v>7050507</v>
+        <v>7050463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1529,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1556,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121374012</v>
+        <v>121373998</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407723</v>
+        <v>407587</v>
       </c>
       <c r="R10" t="n">
-        <v>7050509</v>
+        <v>7050786</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1636,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121373997</v>
+        <v>121373999</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1708,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407494</v>
+        <v>407558</v>
       </c>
       <c r="R11" t="n">
-        <v>7050775</v>
+        <v>7050511</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121374014</v>
+        <v>121374012</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1815,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407751</v>
+        <v>407723</v>
       </c>
       <c r="R12" t="n">
-        <v>7050584</v>
+        <v>7050509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1989,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374022</v>
+        <v>121374011</v>
       </c>
       <c r="B14" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2029,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407793</v>
+        <v>407721</v>
       </c>
       <c r="R14" t="n">
-        <v>7050526</v>
+        <v>7050507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,6 +2060,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374013</v>
+        <v>121374021</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407744</v>
+        <v>407594</v>
       </c>
       <c r="R15" t="n">
-        <v>7050570</v>
+        <v>7050460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,11 +2167,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121374023</v>
+        <v>121374009</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2209,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407746</v>
+        <v>407792</v>
       </c>
       <c r="R16" t="n">
-        <v>7050546</v>
+        <v>7050525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,6 +2269,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374007</v>
+        <v>121374014</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407801</v>
+        <v>407751</v>
       </c>
       <c r="R17" t="n">
-        <v>7050599</v>
+        <v>7050584</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374009</v>
+        <v>121374015</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407792</v>
+        <v>407686</v>
       </c>
       <c r="R18" t="n">
-        <v>7050525</v>
+        <v>7050640</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374021</v>
+        <v>121374013</v>
       </c>
       <c r="B19" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2530,21 +2530,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407594</v>
+        <v>407744</v>
       </c>
       <c r="R19" t="n">
-        <v>7050460</v>
+        <v>7050570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,6 +2590,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,7 +2621,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374004</v>
+        <v>121374000</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2656,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407798</v>
+        <v>407556</v>
       </c>
       <c r="R20" t="n">
-        <v>7050463</v>
+        <v>7050508</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2701,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,7 +2728,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121373999</v>
+        <v>121374007</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2763,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407558</v>
+        <v>407801</v>
       </c>
       <c r="R21" t="n">
-        <v>7050511</v>
+        <v>7050599</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121373998</v>
+        <v>121374023</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,21 +2851,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407587</v>
+        <v>407746</v>
       </c>
       <c r="R22" t="n">
-        <v>7050786</v>
+        <v>7050546</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,11 +2911,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374015</v>
+        <v>121374002</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407686</v>
+        <v>407601</v>
       </c>
       <c r="R23" t="n">
-        <v>7050640</v>
+        <v>7050461</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374002</v>
+        <v>121374017</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407601</v>
+        <v>407695</v>
       </c>
       <c r="R24" t="n">
-        <v>7050461</v>
+        <v>7050648</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374007</v>
+        <v>121374023</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407801</v>
+        <v>407746</v>
       </c>
       <c r="R21" t="n">
-        <v>7050599</v>
+        <v>7050546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,11 +2804,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374023</v>
+        <v>121374007</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407746</v>
+        <v>407801</v>
       </c>
       <c r="R22" t="n">
-        <v>7050546</v>
+        <v>7050599</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,6 +2906,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 46894-2024 artfynd.xlsx
+++ b/artfynd/A 46894-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374022</v>
+        <v>121374017</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407793</v>
+        <v>407695</v>
       </c>
       <c r="R4" t="n">
-        <v>7050526</v>
+        <v>7050648</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,6 +995,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121374001</v>
+        <v>121374022</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407610</v>
+        <v>407793</v>
       </c>
       <c r="R5" t="n">
-        <v>7050459</v>
+        <v>7050526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121374016</v>
+        <v>121374001</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407687</v>
+        <v>407610</v>
       </c>
       <c r="R6" t="n">
-        <v>7050641</v>
+        <v>7050459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121374010</v>
+        <v>121374002</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407753</v>
+        <v>407601</v>
       </c>
       <c r="R7" t="n">
-        <v>7050520</v>
+        <v>7050461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121373997</v>
+        <v>121373999</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407494</v>
+        <v>407558</v>
       </c>
       <c r="R8" t="n">
-        <v>7050775</v>
+        <v>7050511</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121374004</v>
+        <v>121374013</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407798</v>
+        <v>407744</v>
       </c>
       <c r="R9" t="n">
-        <v>7050463</v>
+        <v>7050570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121373998</v>
+        <v>121373997</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407587</v>
+        <v>407494</v>
       </c>
       <c r="R10" t="n">
-        <v>7050786</v>
+        <v>7050775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121373999</v>
+        <v>121374010</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407558</v>
+        <v>407753</v>
       </c>
       <c r="R11" t="n">
-        <v>7050511</v>
+        <v>7050520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121374012</v>
+        <v>121374004</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407723</v>
+        <v>407798</v>
       </c>
       <c r="R12" t="n">
-        <v>7050509</v>
+        <v>7050463</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121374005</v>
+        <v>121374007</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407790</v>
+        <v>407801</v>
       </c>
       <c r="R13" t="n">
-        <v>7050600</v>
+        <v>7050599</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374011</v>
+        <v>121374015</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407721</v>
+        <v>407686</v>
       </c>
       <c r="R14" t="n">
-        <v>7050507</v>
+        <v>7050640</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121374021</v>
+        <v>121374005</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407594</v>
+        <v>407790</v>
       </c>
       <c r="R15" t="n">
-        <v>7050460</v>
+        <v>7050600</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,6 +2167,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121374009</v>
+        <v>121374014</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407792</v>
+        <v>407751</v>
       </c>
       <c r="R16" t="n">
-        <v>7050525</v>
+        <v>7050584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121374014</v>
+        <v>121374021</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407751</v>
+        <v>407594</v>
       </c>
       <c r="R17" t="n">
-        <v>7050584</v>
+        <v>7050460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,11 +2381,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121374015</v>
+        <v>121374023</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407686</v>
+        <v>407746</v>
       </c>
       <c r="R18" t="n">
-        <v>7050640</v>
+        <v>7050546</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,11 +2483,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121374013</v>
+        <v>121374000</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407744</v>
+        <v>407556</v>
       </c>
       <c r="R19" t="n">
-        <v>7050570</v>
+        <v>7050508</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121374000</v>
+        <v>121373998</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2661,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407556</v>
+        <v>407587</v>
       </c>
       <c r="R20" t="n">
-        <v>7050508</v>
+        <v>7050786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2696,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121374023</v>
+        <v>121374011</v>
       </c>
       <c r="B21" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2768,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407746</v>
+        <v>407721</v>
       </c>
       <c r="R21" t="n">
-        <v>7050546</v>
+        <v>7050507</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,6 +2799,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121374007</v>
+        <v>121374012</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407801</v>
+        <v>407723</v>
       </c>
       <c r="R22" t="n">
-        <v>7050599</v>
+        <v>7050509</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121374002</v>
+        <v>121374009</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407601</v>
+        <v>407792</v>
       </c>
       <c r="R23" t="n">
-        <v>7050461</v>
+        <v>7050525</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121374017</v>
+        <v>121374016</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407695</v>
+        <v>407687</v>
       </c>
       <c r="R24" t="n">
-        <v>7050648</v>
+        <v>7050641</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
